--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.68026198862778</v>
+        <v>8.073042573152016</v>
       </c>
       <c r="D2" t="n">
-        <v>49.47793657683967</v>
+        <v>8.040164693736447</v>
       </c>
       <c r="E2" t="n">
-        <v>13.82980482208454</v>
+        <v>2.247343283588739</v>
       </c>
       <c r="F2" t="n">
-        <v>10.41414398489505</v>
+        <v>1.692298397545446</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.27242777378387</v>
+        <v>10.28176951323988</v>
       </c>
       <c r="D3" t="n">
-        <v>63.55359156014927</v>
+        <v>10.32745862852426</v>
       </c>
       <c r="E3" t="n">
-        <v>13.82980482208454</v>
+        <v>2.247343283588739</v>
       </c>
       <c r="F3" t="n">
-        <v>10.41414398489505</v>
+        <v>1.692298397545446</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.59789971130724</v>
+        <v>5.622158703087427</v>
       </c>
       <c r="D4" t="n">
-        <v>34.84712788785039</v>
+        <v>5.662658281775689</v>
       </c>
       <c r="E4" t="n">
-        <v>13.82980482208454</v>
+        <v>2.247343283588739</v>
       </c>
       <c r="F4" t="n">
-        <v>10.41414398489505</v>
+        <v>1.692298397545446</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.47117967999022</v>
+        <v>4.464066697998411</v>
       </c>
       <c r="D5" t="n">
-        <v>54.67627776999966</v>
+        <v>8.884895137624946</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82980482208454</v>
+        <v>2.247343283588739</v>
       </c>
       <c r="F5" t="n">
-        <v>10.41414398489505</v>
+        <v>1.692298397545446</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
